--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.3301</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78.46080000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>207.172</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.3431</v>
+      </c>
+      <c r="G3" t="n">
+        <v>76.2482</v>
+      </c>
+      <c r="H3" t="n">
+        <v>211.2298</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9815</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.4543</v>
+      </c>
+      <c r="G4" t="n">
+        <v>80.4616</v>
+      </c>
+      <c r="H4" t="n">
+        <v>243.0416</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8246</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.9178</v>
+      </c>
+      <c r="G5" t="n">
+        <v>217.1395</v>
+      </c>
+      <c r="H5" t="n">
+        <v>345.4711</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7948</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.8908</v>
+      </c>
+      <c r="G6" t="n">
+        <v>231.8378</v>
+      </c>
+      <c r="H6" t="n">
+        <v>340.3497</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.3693</v>
+      </c>
+      <c r="G7" t="n">
+        <v>79.3674</v>
+      </c>
+      <c r="H7" t="n">
+        <v>219.1526</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9666</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.4155</v>
+      </c>
+      <c r="G8" t="n">
+        <v>101.9202</v>
+      </c>
+      <c r="H8" t="n">
+        <v>232.4302</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.3293</v>
+      </c>
+      <c r="G9" t="n">
+        <v>72.5176</v>
+      </c>
+      <c r="H9" t="n">
+        <v>206.9279</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.4084</v>
+      </c>
+      <c r="G10" t="n">
+        <v>101.6262</v>
+      </c>
+      <c r="H10" t="n">
+        <v>230.4596</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9668</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="G11" t="n">
+        <v>101.6822</v>
+      </c>
+      <c r="H11" t="n">
+        <v>233.423</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9512</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.4218</v>
+      </c>
+      <c r="G12" t="n">
+        <v>120.3965</v>
+      </c>
+      <c r="H12" t="n">
+        <v>234.1957</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9508</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.4236</v>
+      </c>
+      <c r="G13" t="n">
+        <v>120.6718</v>
+      </c>
+      <c r="H13" t="n">
+        <v>234.7091</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9669</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.4195</v>
+      </c>
+      <c r="G14" t="n">
+        <v>101.4023</v>
+      </c>
+      <c r="H14" t="n">
+        <v>233.5611</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9513</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.4185</v>
+      </c>
+      <c r="G15" t="n">
+        <v>120.4701</v>
+      </c>
+      <c r="H15" t="n">
+        <v>233.2755</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.4211</v>
+      </c>
+      <c r="G16" t="n">
+        <v>101.4869</v>
+      </c>
+      <c r="H16" t="n">
+        <v>234.0001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="G17" t="n">
+        <v>121.0278</v>
+      </c>
+      <c r="H17" t="n">
+        <v>234.8054</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.3317</v>
+      </c>
+      <c r="G18" t="n">
+        <v>74.96559999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>207.6785</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.3258</v>
+      </c>
+      <c r="G19" t="n">
+        <v>76.0136</v>
+      </c>
+      <c r="H19" t="n">
+        <v>205.8173</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.3312</v>
+      </c>
+      <c r="G20" t="n">
+        <v>74.6772</v>
+      </c>
+      <c r="H20" t="n">
+        <v>207.5318</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.3413</v>
+      </c>
+      <c r="G21" t="n">
+        <v>76.4205</v>
+      </c>
+      <c r="H21" t="n">
+        <v>210.659</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.3388</v>
+      </c>
+      <c r="G22" t="n">
+        <v>76.6854</v>
+      </c>
+      <c r="H22" t="n">
+        <v>209.8855</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.3366</v>
+      </c>
+      <c r="G23" t="n">
+        <v>79.096</v>
+      </c>
+      <c r="H23" t="n">
+        <v>209.225</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.3407</v>
+      </c>
+      <c r="G24" t="n">
+        <v>77.7834</v>
+      </c>
+      <c r="H24" t="n">
+        <v>210.4819</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.3363</v>
+      </c>
+      <c r="G25" t="n">
+        <v>78.0202</v>
+      </c>
+      <c r="H25" t="n">
+        <v>209.1137</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9847</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.3212</v>
+      </c>
+      <c r="G26" t="n">
+        <v>71.78449999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>204.3829</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.3159</v>
+      </c>
+      <c r="G27" t="n">
+        <v>78.9049</v>
+      </c>
+      <c r="H27" t="n">
+        <v>202.6656</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.3338</v>
+      </c>
+      <c r="G28" t="n">
+        <v>73.9175</v>
+      </c>
+      <c r="H28" t="n">
+        <v>208.3431</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.3327</v>
+      </c>
+      <c r="G29" t="n">
+        <v>75.3237</v>
+      </c>
+      <c r="H29" t="n">
+        <v>207.986</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3333</v>
+      </c>
+      <c r="G30" t="n">
+        <v>74.7431</v>
+      </c>
+      <c r="H30" t="n">
+        <v>208.1763</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.3298</v>
+      </c>
+      <c r="G31" t="n">
+        <v>76.2811</v>
+      </c>
+      <c r="H31" t="n">
+        <v>207.0955</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.3272</v>
+      </c>
+      <c r="G32" t="n">
+        <v>77.38120000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>206.2816</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.3324</v>
+      </c>
+      <c r="G33" t="n">
+        <v>75.9894</v>
+      </c>
+      <c r="H33" t="n">
+        <v>207.904</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.3648</v>
+      </c>
+      <c r="G34" t="n">
+        <v>77.3608</v>
+      </c>
+      <c r="H34" t="n">
+        <v>217.8121</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.3447</v>
+      </c>
+      <c r="G35" t="n">
+        <v>75.93259999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>211.7229</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.3254</v>
+      </c>
+      <c r="G36" t="n">
+        <v>72.556</v>
+      </c>
+      <c r="H36" t="n">
+        <v>205.7174</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.3174</v>
+      </c>
+      <c r="G37" t="n">
+        <v>73.76739999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>203.1489</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.3119</v>
+      </c>
+      <c r="G38" t="n">
+        <v>71.274</v>
+      </c>
+      <c r="H38" t="n">
+        <v>201.3749</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.3277</v>
+      </c>
+      <c r="G39" t="n">
+        <v>73.8531</v>
+      </c>
+      <c r="H39" t="n">
+        <v>206.4336</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.3351</v>
+      </c>
+      <c r="G40" t="n">
+        <v>74.8837</v>
+      </c>
+      <c r="H40" t="n">
+        <v>208.737</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.3641</v>
+      </c>
+      <c r="G41" t="n">
+        <v>77.21680000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>217.5963</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.3454</v>
+      </c>
+      <c r="G42" t="n">
+        <v>75.8536</v>
+      </c>
+      <c r="H42" t="n">
+        <v>211.9246</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.3271</v>
+      </c>
+      <c r="G43" t="n">
+        <v>72.5784</v>
+      </c>
+      <c r="H43" t="n">
+        <v>206.2325</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.3152</v>
+      </c>
+      <c r="G44" t="n">
+        <v>72.11620000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>202.4533</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.3141</v>
+      </c>
+      <c r="G45" t="n">
+        <v>71.3387</v>
+      </c>
+      <c r="H45" t="n">
+        <v>202.1116</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.3294</v>
+      </c>
+      <c r="G46" t="n">
+        <v>73.49630000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>206.9649</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.3378</v>
+      </c>
+      <c r="G47" t="n">
+        <v>75.0603</v>
+      </c>
+      <c r="H47" t="n">
+        <v>209.5983</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="G48" t="n">
+        <v>76.5874</v>
+      </c>
+      <c r="H48" t="n">
+        <v>204.957</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.3218</v>
+      </c>
+      <c r="G49" t="n">
+        <v>73.2556</v>
+      </c>
+      <c r="H49" t="n">
+        <v>204.5618</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9272</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.7853</v>
+      </c>
+      <c r="G50" t="n">
+        <v>165.9978</v>
+      </c>
+      <c r="H50" t="n">
+        <v>319.565</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.8439</v>
+      </c>
+      <c r="G51" t="n">
+        <v>124.7474</v>
+      </c>
+      <c r="H51" t="n">
+        <v>331.2734</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.8567</v>
+      </c>
+      <c r="G52" t="n">
+        <v>123.8721</v>
+      </c>
+      <c r="H52" t="n">
+        <v>333.776</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9704</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.8063</v>
+      </c>
+      <c r="G53" t="n">
+        <v>122.5982</v>
+      </c>
+      <c r="H53" t="n">
+        <v>323.797</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.7918</v>
+      </c>
+      <c r="G54" t="n">
+        <v>116.7749</v>
+      </c>
+      <c r="H54" t="n">
+        <v>320.8805</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9198</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.8424</v>
+      </c>
+      <c r="G55" t="n">
+        <v>184.7439</v>
+      </c>
+      <c r="H55" t="n">
+        <v>330.9797</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9614</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.8754</v>
+      </c>
+      <c r="G56" t="n">
+        <v>150.8007</v>
+      </c>
+      <c r="H56" t="n">
+        <v>337.3909</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.8476</v>
+      </c>
+      <c r="G57" t="n">
+        <v>195.439</v>
+      </c>
+      <c r="H57" t="n">
+        <v>331.9957</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.8919</v>
+      </c>
+      <c r="G58" t="n">
+        <v>215.1202</v>
+      </c>
+      <c r="H58" t="n">
+        <v>340.5587</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.8901</v>
+      </c>
+      <c r="G59" t="n">
+        <v>232.2833</v>
+      </c>
+      <c r="H59" t="n">
+        <v>340.2046</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7943</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.8915</v>
+      </c>
+      <c r="G60" t="n">
+        <v>232.3256</v>
+      </c>
+      <c r="H60" t="n">
+        <v>340.49</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7941</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G61" t="n">
+        <v>232.6417</v>
+      </c>
+      <c r="H61" t="n">
+        <v>340.2002</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8742</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="G62" t="n">
+        <v>199.8669</v>
+      </c>
+      <c r="H62" t="n">
+        <v>327.3299</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.8136</v>
+      </c>
+      <c r="G63" t="n">
+        <v>198.6978</v>
+      </c>
+      <c r="H63" t="n">
+        <v>325.2633</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.8269</v>
+      </c>
+      <c r="G64" t="n">
+        <v>221.0949</v>
+      </c>
+      <c r="H64" t="n">
+        <v>327.9136</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8273</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.8241</v>
+      </c>
+      <c r="G65" t="n">
+        <v>222.1019</v>
+      </c>
+      <c r="H65" t="n">
+        <v>327.3537</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9560999999999999</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.8448</v>
+      </c>
+      <c r="G66" t="n">
+        <v>139.8653</v>
+      </c>
+      <c r="H66" t="n">
+        <v>331.4424</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.8501</v>
+      </c>
+      <c r="G67" t="n">
+        <v>215.3777</v>
+      </c>
+      <c r="H67" t="n">
+        <v>332.4809</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8917</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.8307</v>
+      </c>
+      <c r="G68" t="n">
+        <v>200.0907</v>
+      </c>
+      <c r="H68" t="n">
+        <v>328.6559</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.3609</v>
+      </c>
+      <c r="G69" t="n">
+        <v>77.1288</v>
+      </c>
+      <c r="H69" t="n">
+        <v>216.6438</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.3586</v>
+      </c>
+      <c r="G70" t="n">
+        <v>76.8017</v>
+      </c>
+      <c r="H70" t="n">
+        <v>215.9343</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.3646</v>
+      </c>
+      <c r="G71" t="n">
+        <v>90.1229</v>
+      </c>
+      <c r="H71" t="n">
+        <v>217.7552</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="G72" t="n">
+        <v>76.76649999999999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>218.5758</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.3828</v>
+      </c>
+      <c r="G73" t="n">
+        <v>81.7625</v>
+      </c>
+      <c r="H73" t="n">
+        <v>223.1012</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.3663</v>
+      </c>
+      <c r="G74" t="n">
+        <v>78.6695</v>
+      </c>
+      <c r="H74" t="n">
+        <v>218.2386</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.3769</v>
+      </c>
+      <c r="G75" t="n">
+        <v>94.5852</v>
+      </c>
+      <c r="H75" t="n">
+        <v>221.3754</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.3769</v>
+      </c>
+      <c r="G76" t="n">
+        <v>94.5852</v>
+      </c>
+      <c r="H76" t="n">
+        <v>221.3754</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8747</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.8194</v>
+      </c>
+      <c r="G77" t="n">
+        <v>194.64</v>
+      </c>
+      <c r="H77" t="n">
+        <v>326.4163</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.8232</v>
+      </c>
+      <c r="G78" t="n">
+        <v>194.5315</v>
+      </c>
+      <c r="H78" t="n">
+        <v>327.1773</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.8224</v>
+      </c>
+      <c r="G79" t="n">
+        <v>198.9211</v>
+      </c>
+      <c r="H79" t="n">
+        <v>327.0214</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8753</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.8232</v>
+      </c>
+      <c r="G80" t="n">
+        <v>194.4504</v>
+      </c>
+      <c r="H80" t="n">
+        <v>327.1692</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.8387</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.8378</v>
+      </c>
+      <c r="G81" t="n">
+        <v>222.9703</v>
+      </c>
+      <c r="H81" t="n">
+        <v>330.0651</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9661</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.8188</v>
+      </c>
+      <c r="G82" t="n">
+        <v>124.4302</v>
+      </c>
+      <c r="H82" t="n">
+        <v>326.3032</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.3758</v>
+      </c>
+      <c r="G83" t="n">
+        <v>93.867</v>
+      </c>
+      <c r="H83" t="n">
+        <v>221.0556</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.3764</v>
+      </c>
+      <c r="G84" t="n">
+        <v>81.7243</v>
+      </c>
+      <c r="H84" t="n">
+        <v>221.2451</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.3743</v>
+      </c>
+      <c r="G85" t="n">
+        <v>94.5947</v>
+      </c>
+      <c r="H85" t="n">
+        <v>220.6153</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.3257</v>
+      </c>
+      <c r="G86" t="n">
+        <v>76.4832</v>
+      </c>
+      <c r="H86" t="n">
+        <v>205.8091</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9844000000000001</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="G87" t="n">
+        <v>74.3711</v>
+      </c>
+      <c r="H87" t="n">
+        <v>205.8998</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9842</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.3226</v>
+      </c>
+      <c r="G88" t="n">
+        <v>74.3741</v>
+      </c>
+      <c r="H88" t="n">
+        <v>204.8274</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.3276</v>
+      </c>
+      <c r="G89" t="n">
+        <v>87.6099</v>
+      </c>
+      <c r="H89" t="n">
+        <v>206.3887</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.3272</v>
+      </c>
+      <c r="G90" t="n">
+        <v>72.5485</v>
+      </c>
+      <c r="H90" t="n">
+        <v>206.2654</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="G91" t="n">
+        <v>72.1258</v>
+      </c>
+      <c r="H91" t="n">
+        <v>202.398</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9842</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.3226</v>
+      </c>
+      <c r="G92" t="n">
+        <v>74.3741</v>
+      </c>
+      <c r="H92" t="n">
+        <v>204.8274</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="G93" t="n">
+        <v>72.1258</v>
+      </c>
+      <c r="H93" t="n">
+        <v>202.398</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9815</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.4543</v>
+      </c>
+      <c r="G94" t="n">
+        <v>80.4616</v>
+      </c>
+      <c r="H94" t="n">
+        <v>243.0416</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.0752</v>
+      </c>
+      <c r="G95" t="n">
+        <v>140.2861</v>
+      </c>
+      <c r="H95" t="n">
+        <v>373.919</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9816</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.4547</v>
+      </c>
+      <c r="G96" t="n">
+        <v>80.7573</v>
+      </c>
+      <c r="H96" t="n">
+        <v>243.1735</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9817</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.4585</v>
+      </c>
+      <c r="G97" t="n">
+        <v>80.60599999999999</v>
+      </c>
+      <c r="H97" t="n">
+        <v>244.1827</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.3122</v>
+      </c>
+      <c r="G98" t="n">
+        <v>74.751</v>
+      </c>
+      <c r="H98" t="n">
+        <v>201.4967</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9776</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.2979</v>
+      </c>
+      <c r="G99" t="n">
+        <v>86.697</v>
+      </c>
+      <c r="H99" t="n">
+        <v>196.8098</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G100" t="n">
+        <v>75.1284</v>
+      </c>
+      <c r="H100" t="n">
+        <v>201.4342</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.3307</v>
+      </c>
+      <c r="G101" t="n">
+        <v>79.4743</v>
+      </c>
+      <c r="H101" t="n">
+        <v>207.3863</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="G102" t="n">
+        <v>75.8599</v>
+      </c>
+      <c r="H102" t="n">
+        <v>209.3869</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.3134</v>
+      </c>
+      <c r="G103" t="n">
+        <v>74.60899999999999</v>
+      </c>
+      <c r="H103" t="n">
+        <v>201.869</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.3175</v>
+      </c>
+      <c r="G104" t="n">
+        <v>71.7094</v>
+      </c>
+      <c r="H104" t="n">
+        <v>203.1996</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.3074</v>
+      </c>
+      <c r="G105" t="n">
+        <v>74.0167</v>
+      </c>
+      <c r="H105" t="n">
+        <v>199.9184</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.3076</v>
+      </c>
+      <c r="G106" t="n">
+        <v>77.2214</v>
+      </c>
+      <c r="H106" t="n">
+        <v>200.0079</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.3201</v>
+      </c>
+      <c r="G107" t="n">
+        <v>74.7557</v>
+      </c>
+      <c r="H107" t="n">
+        <v>204.0238</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.3808</v>
+      </c>
+      <c r="G108" t="n">
+        <v>79.8438</v>
+      </c>
+      <c r="H108" t="n">
+        <v>222.5133</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.3592</v>
+      </c>
+      <c r="G109" t="n">
+        <v>77.7732</v>
+      </c>
+      <c r="H109" t="n">
+        <v>216.1284</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.3419</v>
+      </c>
+      <c r="G110" t="n">
+        <v>75.8938</v>
+      </c>
+      <c r="H110" t="n">
+        <v>210.8604</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.3475</v>
+      </c>
+      <c r="G111" t="n">
+        <v>77.86490000000001</v>
+      </c>
+      <c r="H111" t="n">
+        <v>212.569</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.3815</v>
+      </c>
+      <c r="G112" t="n">
+        <v>79.5416</v>
+      </c>
+      <c r="H112" t="n">
+        <v>222.7206</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="G113" t="n">
+        <v>77.8725</v>
+      </c>
+      <c r="H113" t="n">
+        <v>215.7591</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.3424</v>
+      </c>
+      <c r="G114" t="n">
+        <v>75.8768</v>
+      </c>
+      <c r="H114" t="n">
+        <v>211.0035</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.3486</v>
+      </c>
+      <c r="G115" t="n">
+        <v>76.2402</v>
+      </c>
+      <c r="H115" t="n">
+        <v>212.9236</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.8114</v>
+      </c>
+      <c r="G116" t="n">
+        <v>127.1099</v>
+      </c>
+      <c r="H116" t="n">
+        <v>324.8213</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9646</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.8531</v>
+      </c>
+      <c r="G117" t="n">
+        <v>128.7401</v>
+      </c>
+      <c r="H117" t="n">
+        <v>333.0583</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.3074</v>
+      </c>
+      <c r="G118" t="n">
+        <v>74.0167</v>
+      </c>
+      <c r="H118" t="n">
+        <v>199.9184</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="G119" t="n">
+        <v>77.8725</v>
+      </c>
+      <c r="H119" t="n">
+        <v>215.7591</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9789</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.3922</v>
+      </c>
+      <c r="G120" t="n">
+        <v>83.85039999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>225.8438</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9789</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.3922</v>
+      </c>
+      <c r="G121" t="n">
+        <v>83.85039999999999</v>
+      </c>
+      <c r="H121" t="n">
+        <v>225.8438</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.3197</v>
+      </c>
+      <c r="G122" t="n">
+        <v>74.5433</v>
+      </c>
+      <c r="H122" t="n">
+        <v>203.8885</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.3582</v>
+      </c>
+      <c r="G123" t="n">
+        <v>77.87649999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>215.8218</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.338</v>
+      </c>
+      <c r="G124" t="n">
+        <v>74.173</v>
+      </c>
+      <c r="H124" t="n">
+        <v>209.6501</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.3256</v>
+      </c>
+      <c r="G125" t="n">
+        <v>70.88500000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>205.7609</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.3886</v>
+      </c>
+      <c r="G126" t="n">
+        <v>81.38509999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>224.794</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>trans.beta.carotene</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.3289</v>
+      </c>
+      <c r="G127" t="n">
+        <v>72.99979999999999</v>
+      </c>
+      <c r="H127" t="n">
+        <v>206.8062</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9832</v>
+        <v>0.9818</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3301</v>
+        <v>0.6299</v>
       </c>
       <c r="G2" t="n">
-        <v>78.46080000000001</v>
+        <v>79.6758</v>
       </c>
       <c r="H2" t="n">
-        <v>207.172</v>
+        <v>213.6717</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9846</v>
+        <v>0.9772</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3431</v>
+        <v>0.6136</v>
       </c>
       <c r="G3" t="n">
-        <v>76.2482</v>
+        <v>90.441</v>
       </c>
       <c r="H3" t="n">
-        <v>211.2298</v>
+        <v>218.3432</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9815</v>
+        <v>0.9183</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4543</v>
+        <v>0.5444</v>
       </c>
       <c r="G4" t="n">
-        <v>80.4616</v>
+        <v>145.0403</v>
       </c>
       <c r="H4" t="n">
-        <v>243.0416</v>
+        <v>237.083</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8246</v>
+        <v>0.7738</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9178</v>
+        <v>0.1045</v>
       </c>
       <c r="G5" t="n">
-        <v>217.1395</v>
+        <v>237.7742</v>
       </c>
       <c r="H5" t="n">
-        <v>345.4711</v>
+        <v>332.3697</v>
       </c>
     </row>
     <row r="6">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7948</v>
+        <v>0.7762</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8908</v>
+        <v>0.1372</v>
       </c>
       <c r="G6" t="n">
-        <v>231.8378</v>
+        <v>235.0485</v>
       </c>
       <c r="H6" t="n">
-        <v>340.3497</v>
+        <v>326.2506</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3693</v>
+        <v>0.5413</v>
       </c>
       <c r="G7" t="n">
-        <v>79.3674</v>
+        <v>115.3575</v>
       </c>
       <c r="H7" t="n">
-        <v>219.1526</v>
+        <v>237.8895</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9666</v>
+        <v>0.887</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4155</v>
+        <v>0.4904</v>
       </c>
       <c r="G8" t="n">
-        <v>101.9202</v>
+        <v>167.8554</v>
       </c>
       <c r="H8" t="n">
-        <v>232.4302</v>
+        <v>250.736</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9869</v>
+        <v>0.9838</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3293</v>
+        <v>0.639</v>
       </c>
       <c r="G9" t="n">
-        <v>72.5176</v>
+        <v>76.233</v>
       </c>
       <c r="H9" t="n">
-        <v>206.9279</v>
+        <v>211.0472</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9667</v>
+        <v>0.8879</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4084</v>
+        <v>0.4872</v>
       </c>
       <c r="G10" t="n">
-        <v>101.6262</v>
+        <v>167.3157</v>
       </c>
       <c r="H10" t="n">
-        <v>230.4596</v>
+        <v>251.5285</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9668</v>
+        <v>0.8871</v>
       </c>
       <c r="F11" t="n">
-        <v>1.419</v>
+        <v>0.4905</v>
       </c>
       <c r="G11" t="n">
-        <v>101.6822</v>
+        <v>167.9084</v>
       </c>
       <c r="H11" t="n">
-        <v>233.423</v>
+        <v>250.7087</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9512</v>
+        <v>0.9112</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4218</v>
+        <v>0.4917</v>
       </c>
       <c r="G12" t="n">
-        <v>120.3965</v>
+        <v>150.0437</v>
       </c>
       <c r="H12" t="n">
-        <v>234.1957</v>
+        <v>250.4246</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9508</v>
+        <v>0.8873</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4236</v>
+        <v>0.4906</v>
       </c>
       <c r="G13" t="n">
-        <v>120.6718</v>
+        <v>167.7</v>
       </c>
       <c r="H13" t="n">
-        <v>234.7091</v>
+        <v>250.6874</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9669</v>
+        <v>0.8875</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4195</v>
+        <v>0.4904</v>
       </c>
       <c r="G14" t="n">
-        <v>101.4023</v>
+        <v>167.6764</v>
       </c>
       <c r="H14" t="n">
-        <v>233.5611</v>
+        <v>250.7392</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9513</v>
+        <v>0.8868</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4185</v>
+        <v>0.4904</v>
       </c>
       <c r="G15" t="n">
-        <v>120.4701</v>
+        <v>168.0572</v>
       </c>
       <c r="H15" t="n">
-        <v>233.2755</v>
+        <v>250.7425</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.967</v>
+        <v>0.8868</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4211</v>
+        <v>0.4913</v>
       </c>
       <c r="G16" t="n">
-        <v>101.4869</v>
+        <v>168.0465</v>
       </c>
       <c r="H16" t="n">
-        <v>234.0001</v>
+        <v>250.5222</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9505</v>
+        <v>0.9072</v>
       </c>
       <c r="F17" t="n">
-        <v>1.424</v>
+        <v>0.4929</v>
       </c>
       <c r="G17" t="n">
-        <v>121.0278</v>
+        <v>152.3368</v>
       </c>
       <c r="H17" t="n">
-        <v>234.8054</v>
+        <v>250.1236</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9846</v>
+        <v>0.9728</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3317</v>
+        <v>0.612</v>
       </c>
       <c r="G18" t="n">
-        <v>74.96559999999999</v>
+        <v>92.76600000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>207.6785</v>
+        <v>218.7833</v>
       </c>
     </row>
     <row r="19">
@@ -1022,16 +1022,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9831</v>
+        <v>0.9802</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3258</v>
+        <v>0.6119</v>
       </c>
       <c r="G19" t="n">
-        <v>76.0136</v>
+        <v>78.3843</v>
       </c>
       <c r="H19" t="n">
-        <v>205.8173</v>
+        <v>218.8132</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9839</v>
+        <v>0.9584</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3312</v>
+        <v>0.6088</v>
       </c>
       <c r="G20" t="n">
-        <v>74.6772</v>
+        <v>111.3728</v>
       </c>
       <c r="H20" t="n">
-        <v>207.5318</v>
+        <v>219.6773</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9833</v>
+        <v>0.9802</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3413</v>
+        <v>0.609</v>
       </c>
       <c r="G21" t="n">
-        <v>76.4205</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>210.659</v>
+        <v>219.6314</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9831</v>
+        <v>0.9721</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3388</v>
+        <v>0.6057</v>
       </c>
       <c r="G22" t="n">
-        <v>76.6854</v>
+        <v>94.8904</v>
       </c>
       <c r="H22" t="n">
-        <v>209.8855</v>
+        <v>220.5582</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9825</v>
+        <v>0.9728</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3366</v>
+        <v>0.5996</v>
       </c>
       <c r="G23" t="n">
-        <v>79.096</v>
+        <v>94.18899999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>209.225</v>
+        <v>222.254</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9825</v>
+        <v>0.9714</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3407</v>
+        <v>0.5991</v>
       </c>
       <c r="G24" t="n">
-        <v>77.7834</v>
+        <v>93.559</v>
       </c>
       <c r="H24" t="n">
-        <v>210.4819</v>
+        <v>222.3952</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9729</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3363</v>
+        <v>0.6038</v>
       </c>
       <c r="G25" t="n">
-        <v>78.0202</v>
+        <v>91.2242</v>
       </c>
       <c r="H25" t="n">
-        <v>209.1137</v>
+        <v>221.0815</v>
       </c>
     </row>
     <row r="26">
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9847</v>
+        <v>0.9833</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3212</v>
+        <v>0.6243</v>
       </c>
       <c r="G26" t="n">
-        <v>71.78449999999999</v>
+        <v>74.18819999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>204.3829</v>
+        <v>215.291</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9837</v>
+        <v>0.9832</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3159</v>
+        <v>0.6173</v>
       </c>
       <c r="G27" t="n">
-        <v>78.9049</v>
+        <v>77.087</v>
       </c>
       <c r="H27" t="n">
-        <v>202.6656</v>
+        <v>217.2857</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9846</v>
+        <v>0.973</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3338</v>
+        <v>0.6189</v>
       </c>
       <c r="G28" t="n">
-        <v>73.9175</v>
+        <v>92.742</v>
       </c>
       <c r="H28" t="n">
-        <v>208.3431</v>
+        <v>216.8342</v>
       </c>
     </row>
     <row r="29">
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9838</v>
+        <v>0.9823</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3327</v>
+        <v>0.6087</v>
       </c>
       <c r="G29" t="n">
-        <v>75.3237</v>
+        <v>77.4255</v>
       </c>
       <c r="H29" t="n">
-        <v>207.986</v>
+        <v>219.7015</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9841</v>
+        <v>0.9804</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3333</v>
+        <v>0.6143</v>
       </c>
       <c r="G30" t="n">
-        <v>74.7431</v>
+        <v>78.2304</v>
       </c>
       <c r="H30" t="n">
-        <v>208.1763</v>
+        <v>218.1481</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9833</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3298</v>
+        <v>0.5948</v>
       </c>
       <c r="G31" t="n">
-        <v>76.2811</v>
+        <v>94.7642</v>
       </c>
       <c r="H31" t="n">
-        <v>207.0955</v>
+        <v>223.5735</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9837</v>
+        <v>0.9576</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3272</v>
+        <v>0.5989</v>
       </c>
       <c r="G32" t="n">
-        <v>77.38120000000001</v>
+        <v>112.2128</v>
       </c>
       <c r="H32" t="n">
-        <v>206.2816</v>
+        <v>222.4398</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9836</v>
+        <v>0.973</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3324</v>
+        <v>0.598</v>
       </c>
       <c r="G33" t="n">
-        <v>75.9894</v>
+        <v>94.85890000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>207.904</v>
+        <v>222.6858</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9852</v>
+        <v>0.9858</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3648</v>
+        <v>0.6025</v>
       </c>
       <c r="G34" t="n">
-        <v>77.3608</v>
+        <v>79.7694</v>
       </c>
       <c r="H34" t="n">
-        <v>217.8121</v>
+        <v>221.4493</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9862</v>
+        <v>0.9787</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3447</v>
+        <v>0.619</v>
       </c>
       <c r="G35" t="n">
-        <v>75.93259999999999</v>
+        <v>87.9725</v>
       </c>
       <c r="H35" t="n">
-        <v>211.7229</v>
+        <v>216.8021</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9871</v>
+        <v>0.984</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3254</v>
+        <v>0.6302</v>
       </c>
       <c r="G36" t="n">
-        <v>72.556</v>
+        <v>75.2931</v>
       </c>
       <c r="H36" t="n">
-        <v>205.7174</v>
+        <v>213.5787</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9869</v>
+        <v>0.9796</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3174</v>
+        <v>0.6338</v>
       </c>
       <c r="G37" t="n">
-        <v>73.76739999999999</v>
+        <v>83.85939999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>203.1489</v>
+        <v>212.5553</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9865</v>
+        <v>0.9835</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3119</v>
+        <v>0.6392</v>
       </c>
       <c r="G38" t="n">
-        <v>71.274</v>
+        <v>76.32559999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>201.3749</v>
+        <v>210.9786</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9848</v>
+        <v>0.9787</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3277</v>
+        <v>0.6133</v>
       </c>
       <c r="G39" t="n">
-        <v>73.8531</v>
+        <v>85.00660000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>206.4336</v>
+        <v>218.4191</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9845</v>
+        <v>0.9825</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3351</v>
+        <v>0.6096</v>
       </c>
       <c r="G40" t="n">
-        <v>74.8837</v>
+        <v>77.4571</v>
       </c>
       <c r="H40" t="n">
-        <v>208.737</v>
+        <v>219.4578</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9853</v>
+        <v>0.9858</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3641</v>
+        <v>0.5992</v>
       </c>
       <c r="G41" t="n">
-        <v>77.21680000000001</v>
+        <v>79.6913</v>
       </c>
       <c r="H41" t="n">
-        <v>217.5963</v>
+        <v>222.3615</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9862</v>
+        <v>0.9787</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3454</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>75.8536</v>
+        <v>88.0277</v>
       </c>
       <c r="H42" t="n">
-        <v>211.9246</v>
+        <v>216.9771</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9872</v>
+        <v>0.9846</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3271</v>
+        <v>0.631</v>
       </c>
       <c r="G43" t="n">
-        <v>72.5784</v>
+        <v>75.1566</v>
       </c>
       <c r="H43" t="n">
-        <v>206.2325</v>
+        <v>213.3625</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9767</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3152</v>
+        <v>0.635</v>
       </c>
       <c r="G44" t="n">
-        <v>72.11620000000001</v>
+        <v>87.8403</v>
       </c>
       <c r="H44" t="n">
-        <v>202.4533</v>
+        <v>212.1995</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9838</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3141</v>
+        <v>0.6413</v>
       </c>
       <c r="G45" t="n">
-        <v>71.3387</v>
+        <v>76.75190000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>202.1116</v>
+        <v>210.3563</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9848</v>
+        <v>0.9787</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3294</v>
+        <v>0.6231</v>
       </c>
       <c r="G46" t="n">
-        <v>73.49630000000001</v>
+        <v>85.7784</v>
       </c>
       <c r="H46" t="n">
-        <v>206.9649</v>
+        <v>215.6314</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9843</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3378</v>
+        <v>0.613</v>
       </c>
       <c r="G47" t="n">
-        <v>75.0603</v>
+        <v>91.94970000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>209.5983</v>
+        <v>218.5152</v>
       </c>
     </row>
     <row r="48">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.985</v>
+        <v>0.9841</v>
       </c>
       <c r="F48" t="n">
-        <v>1.323</v>
+        <v>0.6244</v>
       </c>
       <c r="G48" t="n">
-        <v>76.5874</v>
+        <v>74.58540000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>204.957</v>
+        <v>215.2607</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9865</v>
+        <v>0.9839</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3218</v>
+        <v>0.6333</v>
       </c>
       <c r="G49" t="n">
-        <v>73.2556</v>
+        <v>77.1825</v>
       </c>
       <c r="H49" t="n">
-        <v>204.5618</v>
+        <v>212.6855</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9272</v>
+        <v>0.9596</v>
       </c>
       <c r="F50" t="n">
-        <v>1.7853</v>
+        <v>0.1454</v>
       </c>
       <c r="G50" t="n">
-        <v>165.9978</v>
+        <v>135.2762</v>
       </c>
       <c r="H50" t="n">
-        <v>319.565</v>
+        <v>324.7046</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9625</v>
+        <v>0.8225</v>
       </c>
       <c r="F51" t="n">
-        <v>1.8439</v>
+        <v>0.1026</v>
       </c>
       <c r="G51" t="n">
-        <v>124.7474</v>
+        <v>225.2909</v>
       </c>
       <c r="H51" t="n">
-        <v>331.2734</v>
+        <v>332.7389</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.967</v>
+        <v>0.8124</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8567</v>
+        <v>0.113</v>
       </c>
       <c r="G52" t="n">
-        <v>123.8721</v>
+        <v>228.5872</v>
       </c>
       <c r="H52" t="n">
-        <v>333.776</v>
+        <v>330.7946</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9704</v>
+        <v>0.9181</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8063</v>
+        <v>0.1466</v>
       </c>
       <c r="G53" t="n">
-        <v>122.5982</v>
+        <v>173.7932</v>
       </c>
       <c r="H53" t="n">
-        <v>323.797</v>
+        <v>324.4811</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9697</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>1.7918</v>
+        <v>0.171</v>
       </c>
       <c r="G54" t="n">
-        <v>116.7749</v>
+        <v>180.3647</v>
       </c>
       <c r="H54" t="n">
-        <v>320.8805</v>
+        <v>319.8003</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9198</v>
+        <v>0.8726</v>
       </c>
       <c r="F55" t="n">
-        <v>1.8424</v>
+        <v>0.0493</v>
       </c>
       <c r="G55" t="n">
-        <v>184.7439</v>
+        <v>221.4683</v>
       </c>
       <c r="H55" t="n">
-        <v>330.9797</v>
+        <v>342.4732</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9614</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>1.8754</v>
+        <v>0.0522</v>
       </c>
       <c r="G56" t="n">
-        <v>150.8007</v>
+        <v>213.2395</v>
       </c>
       <c r="H56" t="n">
-        <v>337.3909</v>
+        <v>341.9535</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.892</v>
+        <v>0.8966</v>
       </c>
       <c r="F57" t="n">
-        <v>1.8476</v>
+        <v>0.1019</v>
       </c>
       <c r="G57" t="n">
-        <v>195.439</v>
+        <v>192.6869</v>
       </c>
       <c r="H57" t="n">
-        <v>331.9957</v>
+        <v>332.8668</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.83</v>
+        <v>0.7759</v>
       </c>
       <c r="F58" t="n">
-        <v>1.8919</v>
+        <v>0.1409</v>
       </c>
       <c r="G58" t="n">
-        <v>215.1202</v>
+        <v>235.3375</v>
       </c>
       <c r="H58" t="n">
-        <v>340.5587</v>
+        <v>325.5596</v>
       </c>
     </row>
     <row r="59">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.7945</v>
+        <v>0.7743</v>
       </c>
       <c r="F59" t="n">
-        <v>1.8901</v>
+        <v>0.1403</v>
       </c>
       <c r="G59" t="n">
-        <v>232.2833</v>
+        <v>235.7789</v>
       </c>
       <c r="H59" t="n">
-        <v>340.2046</v>
+        <v>325.671</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7943</v>
+        <v>0.8153</v>
       </c>
       <c r="F60" t="n">
-        <v>1.8915</v>
+        <v>0.1413</v>
       </c>
       <c r="G60" t="n">
-        <v>232.3256</v>
+        <v>218.3655</v>
       </c>
       <c r="H60" t="n">
-        <v>340.49</v>
+        <v>325.4746</v>
       </c>
     </row>
     <row r="61">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.7941</v>
+        <v>0.774</v>
       </c>
       <c r="F61" t="n">
-        <v>1.89</v>
+        <v>0.1404</v>
       </c>
       <c r="G61" t="n">
-        <v>232.6417</v>
+        <v>235.6484</v>
       </c>
       <c r="H61" t="n">
-        <v>340.2002</v>
+        <v>325.6433</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8742</v>
+        <v>0.8607</v>
       </c>
       <c r="F62" t="n">
-        <v>1.824</v>
+        <v>0.1474</v>
       </c>
       <c r="G62" t="n">
-        <v>199.8669</v>
+        <v>202.4866</v>
       </c>
       <c r="H62" t="n">
-        <v>327.3299</v>
+        <v>324.3184</v>
       </c>
     </row>
     <row r="63">
@@ -2430,16 +2430,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8729</v>
+        <v>0.8556</v>
       </c>
       <c r="F63" t="n">
-        <v>1.8136</v>
+        <v>0.1461</v>
       </c>
       <c r="G63" t="n">
-        <v>198.6978</v>
+        <v>204.4615</v>
       </c>
       <c r="H63" t="n">
-        <v>325.2633</v>
+        <v>324.5707</v>
       </c>
     </row>
     <row r="64">
@@ -2462,16 +2462,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8174</v>
       </c>
       <c r="F64" t="n">
-        <v>1.8269</v>
+        <v>0.15</v>
       </c>
       <c r="G64" t="n">
-        <v>221.0949</v>
+        <v>225.3542</v>
       </c>
       <c r="H64" t="n">
-        <v>327.9136</v>
+        <v>323.8182</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8273</v>
+        <v>0.8269</v>
       </c>
       <c r="F65" t="n">
-        <v>1.8241</v>
+        <v>0.1595</v>
       </c>
       <c r="G65" t="n">
-        <v>222.1019</v>
+        <v>219.0303</v>
       </c>
       <c r="H65" t="n">
-        <v>327.3537</v>
+        <v>322.0183</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.8627</v>
       </c>
       <c r="F66" t="n">
-        <v>1.8448</v>
+        <v>0.0931</v>
       </c>
       <c r="G66" t="n">
-        <v>139.8653</v>
+        <v>218.4071</v>
       </c>
       <c r="H66" t="n">
-        <v>331.4424</v>
+        <v>334.496</v>
       </c>
     </row>
     <row r="67">
@@ -2558,16 +2558,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8704</v>
+        <v>0.8673</v>
       </c>
       <c r="F67" t="n">
-        <v>1.8501</v>
+        <v>0.1155</v>
       </c>
       <c r="G67" t="n">
-        <v>215.3777</v>
+        <v>218.1461</v>
       </c>
       <c r="H67" t="n">
-        <v>332.4809</v>
+        <v>330.3318</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8917</v>
+        <v>0.8828</v>
       </c>
       <c r="F68" t="n">
-        <v>1.8307</v>
+        <v>0.0997</v>
       </c>
       <c r="G68" t="n">
-        <v>200.0907</v>
+        <v>209.3489</v>
       </c>
       <c r="H68" t="n">
-        <v>328.6559</v>
+        <v>333.2677</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9829</v>
+        <v>0.9554</v>
       </c>
       <c r="F69" t="n">
-        <v>1.3609</v>
+        <v>0.593</v>
       </c>
       <c r="G69" t="n">
-        <v>77.1288</v>
+        <v>114.6712</v>
       </c>
       <c r="H69" t="n">
-        <v>216.6438</v>
+        <v>224.0827</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9828</v>
+        <v>0.9697</v>
       </c>
       <c r="F70" t="n">
-        <v>1.3586</v>
+        <v>0.5823</v>
       </c>
       <c r="G70" t="n">
-        <v>76.8017</v>
+        <v>97.2319</v>
       </c>
       <c r="H70" t="n">
-        <v>215.9343</v>
+        <v>227.0171</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9764</v>
+        <v>0.9754</v>
       </c>
       <c r="F71" t="n">
-        <v>1.3646</v>
+        <v>0.6029</v>
       </c>
       <c r="G71" t="n">
-        <v>90.1229</v>
+        <v>87.7278</v>
       </c>
       <c r="H71" t="n">
-        <v>217.7552</v>
+        <v>221.3476</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9829</v>
+        <v>0.9737</v>
       </c>
       <c r="F72" t="n">
-        <v>1.3674</v>
+        <v>0.5901</v>
       </c>
       <c r="G72" t="n">
-        <v>76.76649999999999</v>
+        <v>90.77849999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>218.5758</v>
+        <v>224.8766</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.984</v>
+        <v>0.9835</v>
       </c>
       <c r="F73" t="n">
-        <v>1.3828</v>
+        <v>0.5769</v>
       </c>
       <c r="G73" t="n">
-        <v>81.7625</v>
+        <v>80.56399999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>223.1012</v>
+        <v>228.4727</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.984</v>
+        <v>0.9835</v>
       </c>
       <c r="F74" t="n">
-        <v>1.3663</v>
+        <v>0.5834</v>
       </c>
       <c r="G74" t="n">
-        <v>78.6695</v>
+        <v>78.06780000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>218.2386</v>
+        <v>226.7052</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9724</v>
+        <v>0.9429</v>
       </c>
       <c r="F75" t="n">
-        <v>1.3769</v>
+        <v>0.5464</v>
       </c>
       <c r="G75" t="n">
-        <v>94.5852</v>
+        <v>124.2205</v>
       </c>
       <c r="H75" t="n">
-        <v>221.3754</v>
+        <v>236.5447</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9724</v>
+        <v>0.9429</v>
       </c>
       <c r="F76" t="n">
-        <v>1.3769</v>
+        <v>0.5464</v>
       </c>
       <c r="G76" t="n">
-        <v>94.5852</v>
+        <v>124.2205</v>
       </c>
       <c r="H76" t="n">
-        <v>221.3754</v>
+        <v>236.5447</v>
       </c>
     </row>
     <row r="77">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8747</v>
+        <v>0.8544</v>
       </c>
       <c r="F77" t="n">
-        <v>1.8194</v>
+        <v>0.1333</v>
       </c>
       <c r="G77" t="n">
-        <v>194.64</v>
+        <v>200.5834</v>
       </c>
       <c r="H77" t="n">
-        <v>326.4163</v>
+        <v>326.9984</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8751</v>
+        <v>0.8595</v>
       </c>
       <c r="F78" t="n">
-        <v>1.8232</v>
+        <v>0.1328</v>
       </c>
       <c r="G78" t="n">
-        <v>194.5315</v>
+        <v>199.1618</v>
       </c>
       <c r="H78" t="n">
-        <v>327.1773</v>
+        <v>327.077</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8667</v>
+        <v>0.8253</v>
       </c>
       <c r="F79" t="n">
-        <v>1.8224</v>
+        <v>0.1324</v>
       </c>
       <c r="G79" t="n">
-        <v>198.9211</v>
+        <v>214.4982</v>
       </c>
       <c r="H79" t="n">
-        <v>327.0214</v>
+        <v>327.1577</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8753</v>
+        <v>0.8596</v>
       </c>
       <c r="F80" t="n">
-        <v>1.8232</v>
+        <v>0.1315</v>
       </c>
       <c r="G80" t="n">
-        <v>194.4504</v>
+        <v>199.2548</v>
       </c>
       <c r="H80" t="n">
-        <v>327.1692</v>
+        <v>327.3221</v>
       </c>
     </row>
     <row r="81">
@@ -3006,16 +3006,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8387</v>
+        <v>0.8282</v>
       </c>
       <c r="F81" t="n">
-        <v>1.8378</v>
+        <v>0.1116</v>
       </c>
       <c r="G81" t="n">
-        <v>222.9703</v>
+        <v>225.7096</v>
       </c>
       <c r="H81" t="n">
-        <v>330.0651</v>
+        <v>331.0557</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9661</v>
+        <v>0.8184</v>
       </c>
       <c r="F82" t="n">
-        <v>1.8188</v>
+        <v>0.1086</v>
       </c>
       <c r="G82" t="n">
-        <v>124.4302</v>
+        <v>228.091</v>
       </c>
       <c r="H82" t="n">
-        <v>326.3032</v>
+        <v>331.612</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9727</v>
+        <v>0.946</v>
       </c>
       <c r="F83" t="n">
-        <v>1.3758</v>
+        <v>0.5411</v>
       </c>
       <c r="G83" t="n">
-        <v>93.867</v>
+        <v>121.9193</v>
       </c>
       <c r="H83" t="n">
-        <v>221.0556</v>
+        <v>237.9314</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.98</v>
+        <v>0.9463</v>
       </c>
       <c r="F84" t="n">
-        <v>1.3764</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>81.7243</v>
+        <v>121.6316</v>
       </c>
       <c r="H84" t="n">
-        <v>221.2451</v>
+        <v>238.2687</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9722</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>1.3743</v>
+        <v>0.542</v>
       </c>
       <c r="G85" t="n">
-        <v>94.5947</v>
+        <v>121.9263</v>
       </c>
       <c r="H85" t="n">
-        <v>220.6153</v>
+        <v>237.7052</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.984</v>
+        <v>0.9727</v>
       </c>
       <c r="F86" t="n">
-        <v>1.3257</v>
+        <v>0.6251</v>
       </c>
       <c r="G86" t="n">
-        <v>76.4832</v>
+        <v>91.0848</v>
       </c>
       <c r="H86" t="n">
-        <v>205.8091</v>
+        <v>215.0679</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9797</v>
       </c>
       <c r="F87" t="n">
-        <v>1.326</v>
+        <v>0.6163</v>
       </c>
       <c r="G87" t="n">
-        <v>74.3711</v>
+        <v>81.4692</v>
       </c>
       <c r="H87" t="n">
-        <v>205.8998</v>
+        <v>217.5826</v>
       </c>
     </row>
     <row r="88">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9842</v>
+        <v>0.9821</v>
       </c>
       <c r="F88" t="n">
-        <v>1.3226</v>
+        <v>0.6113</v>
       </c>
       <c r="G88" t="n">
-        <v>74.3741</v>
+        <v>78.1208</v>
       </c>
       <c r="H88" t="n">
-        <v>204.8274</v>
+        <v>218.968</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.977</v>
+        <v>0.9728</v>
       </c>
       <c r="F89" t="n">
-        <v>1.3276</v>
+        <v>0.6119</v>
       </c>
       <c r="G89" t="n">
-        <v>87.6099</v>
+        <v>94.5587</v>
       </c>
       <c r="H89" t="n">
-        <v>206.3887</v>
+        <v>218.8015</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9872</v>
+        <v>0.9845</v>
       </c>
       <c r="F90" t="n">
-        <v>1.3272</v>
+        <v>0.6311</v>
       </c>
       <c r="G90" t="n">
-        <v>72.5485</v>
+        <v>75.2604</v>
       </c>
       <c r="H90" t="n">
-        <v>206.2654</v>
+        <v>213.3391</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9767</v>
       </c>
       <c r="F91" t="n">
-        <v>1.315</v>
+        <v>0.6352</v>
       </c>
       <c r="G91" t="n">
-        <v>72.1258</v>
+        <v>87.8403</v>
       </c>
       <c r="H91" t="n">
-        <v>202.398</v>
+        <v>212.134</v>
       </c>
     </row>
     <row r="92">
@@ -3358,16 +3358,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9842</v>
+        <v>0.9821</v>
       </c>
       <c r="F92" t="n">
-        <v>1.3226</v>
+        <v>0.6113</v>
       </c>
       <c r="G92" t="n">
-        <v>74.3741</v>
+        <v>78.1208</v>
       </c>
       <c r="H92" t="n">
-        <v>204.8274</v>
+        <v>218.968</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9767</v>
       </c>
       <c r="F93" t="n">
-        <v>1.315</v>
+        <v>0.6352</v>
       </c>
       <c r="G93" t="n">
-        <v>72.1258</v>
+        <v>87.8403</v>
       </c>
       <c r="H93" t="n">
-        <v>202.398</v>
+        <v>212.134</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9815</v>
+        <v>0.9183</v>
       </c>
       <c r="F94" t="n">
-        <v>1.4543</v>
+        <v>0.5444</v>
       </c>
       <c r="G94" t="n">
-        <v>80.4616</v>
+        <v>145.0403</v>
       </c>
       <c r="H94" t="n">
-        <v>243.0416</v>
+        <v>237.083</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.9549</v>
+        <v>0.9398</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0752</v>
+        <v>-0.1016</v>
       </c>
       <c r="G95" t="n">
-        <v>140.2861</v>
+        <v>171.2707</v>
       </c>
       <c r="H95" t="n">
-        <v>373.919</v>
+        <v>368.6547</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9816</v>
+        <v>0.918</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4547</v>
+        <v>0.5474</v>
       </c>
       <c r="G96" t="n">
-        <v>80.7573</v>
+        <v>145.1622</v>
       </c>
       <c r="H96" t="n">
-        <v>243.1735</v>
+        <v>236.3011</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9817</v>
+        <v>0.9173</v>
       </c>
       <c r="F97" t="n">
-        <v>1.4585</v>
+        <v>0.5493</v>
       </c>
       <c r="G97" t="n">
-        <v>80.60599999999999</v>
+        <v>145.5343</v>
       </c>
       <c r="H97" t="n">
-        <v>244.1827</v>
+        <v>235.8059</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9846</v>
+        <v>0.9767</v>
       </c>
       <c r="F98" t="n">
-        <v>1.3122</v>
+        <v>0.6325</v>
       </c>
       <c r="G98" t="n">
-        <v>74.751</v>
+        <v>86.8313</v>
       </c>
       <c r="H98" t="n">
-        <v>201.4967</v>
+        <v>212.9363</v>
       </c>
     </row>
     <row r="99">
@@ -3582,16 +3582,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9776</v>
+        <v>0.9696</v>
       </c>
       <c r="F99" t="n">
-        <v>1.2979</v>
+        <v>0.6377</v>
       </c>
       <c r="G99" t="n">
-        <v>86.697</v>
+        <v>93.6326</v>
       </c>
       <c r="H99" t="n">
-        <v>196.8098</v>
+        <v>211.4112</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.984</v>
+        <v>0.9731</v>
       </c>
       <c r="F100" t="n">
-        <v>1.312</v>
+        <v>0.622</v>
       </c>
       <c r="G100" t="n">
-        <v>75.1284</v>
+        <v>92.47280000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>201.4342</v>
+        <v>215.9427</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9815</v>
       </c>
       <c r="F101" t="n">
-        <v>1.3307</v>
+        <v>0.6078</v>
       </c>
       <c r="G101" t="n">
-        <v>79.4743</v>
+        <v>80.4408</v>
       </c>
       <c r="H101" t="n">
-        <v>207.3863</v>
+        <v>219.9636</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9833</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3372</v>
+        <v>0.6034</v>
       </c>
       <c r="G102" t="n">
-        <v>75.8599</v>
+        <v>81.0034</v>
       </c>
       <c r="H102" t="n">
-        <v>209.3869</v>
+        <v>221.19</v>
       </c>
     </row>
     <row r="103">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9852</v>
+        <v>0.9798</v>
       </c>
       <c r="F103" t="n">
-        <v>1.3134</v>
+        <v>0.6344</v>
       </c>
       <c r="G103" t="n">
-        <v>74.60899999999999</v>
+        <v>79.3028</v>
       </c>
       <c r="H103" t="n">
-        <v>201.869</v>
+        <v>212.3663</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9851</v>
+        <v>0.9775</v>
       </c>
       <c r="F104" t="n">
-        <v>1.3175</v>
+        <v>0.6272</v>
       </c>
       <c r="G104" t="n">
-        <v>71.7094</v>
+        <v>85.04949999999999</v>
       </c>
       <c r="H104" t="n">
-        <v>203.1996</v>
+        <v>214.4576</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9848</v>
+        <v>0.9716</v>
       </c>
       <c r="F105" t="n">
-        <v>1.3074</v>
+        <v>0.6337</v>
       </c>
       <c r="G105" t="n">
-        <v>74.0167</v>
+        <v>90.50620000000001</v>
       </c>
       <c r="H105" t="n">
-        <v>199.9184</v>
+        <v>212.5833</v>
       </c>
     </row>
     <row r="106">
@@ -3806,16 +3806,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9829</v>
+        <v>0.9785</v>
       </c>
       <c r="F106" t="n">
-        <v>1.3076</v>
+        <v>0.6375</v>
       </c>
       <c r="G106" t="n">
-        <v>77.2214</v>
+        <v>80.7516</v>
       </c>
       <c r="H106" t="n">
-        <v>200.0079</v>
+        <v>211.4601</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9846</v>
+        <v>0.9748</v>
       </c>
       <c r="F107" t="n">
-        <v>1.3201</v>
+        <v>0.6138</v>
       </c>
       <c r="G107" t="n">
-        <v>74.7557</v>
+        <v>89.4128</v>
       </c>
       <c r="H107" t="n">
-        <v>204.0238</v>
+        <v>218.2727</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.976</v>
       </c>
       <c r="F108" t="n">
-        <v>1.3808</v>
+        <v>0.5873</v>
       </c>
       <c r="G108" t="n">
-        <v>79.8438</v>
+        <v>92.63209999999999</v>
       </c>
       <c r="H108" t="n">
-        <v>222.5133</v>
+        <v>225.6395</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9867</v>
+        <v>0.9732</v>
       </c>
       <c r="F109" t="n">
-        <v>1.3592</v>
+        <v>0.6022</v>
       </c>
       <c r="G109" t="n">
-        <v>77.7732</v>
+        <v>96.7359</v>
       </c>
       <c r="H109" t="n">
-        <v>216.1284</v>
+        <v>221.5222</v>
       </c>
     </row>
     <row r="110">
@@ -3934,16 +3934,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9846</v>
+        <v>0.982</v>
       </c>
       <c r="F110" t="n">
-        <v>1.3419</v>
+        <v>0.6439</v>
       </c>
       <c r="G110" t="n">
-        <v>75.8938</v>
+        <v>79.0462</v>
       </c>
       <c r="H110" t="n">
-        <v>210.8604</v>
+        <v>209.6004</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9856</v>
+        <v>0.9835</v>
       </c>
       <c r="F111" t="n">
-        <v>1.3475</v>
+        <v>0.601</v>
       </c>
       <c r="G111" t="n">
-        <v>77.86490000000001</v>
+        <v>78.81100000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>212.569</v>
+        <v>221.8662</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9856</v>
+        <v>0.9757</v>
       </c>
       <c r="F112" t="n">
-        <v>1.3815</v>
+        <v>0.5863</v>
       </c>
       <c r="G112" t="n">
-        <v>79.5416</v>
+        <v>92.9205</v>
       </c>
       <c r="H112" t="n">
-        <v>222.7206</v>
+        <v>225.9277</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9867</v>
+        <v>0.9822</v>
       </c>
       <c r="F113" t="n">
-        <v>1.358</v>
+        <v>0.6054</v>
       </c>
       <c r="G113" t="n">
-        <v>77.8725</v>
+        <v>81.03100000000001</v>
       </c>
       <c r="H113" t="n">
-        <v>215.7591</v>
+        <v>220.6248</v>
       </c>
     </row>
     <row r="114">
@@ -4062,16 +4062,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9848</v>
+        <v>0.9815</v>
       </c>
       <c r="F114" t="n">
-        <v>1.3424</v>
+        <v>0.647</v>
       </c>
       <c r="G114" t="n">
-        <v>75.8768</v>
+        <v>79.49760000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>211.0035</v>
+        <v>208.6895</v>
       </c>
     </row>
     <row r="115">
@@ -4094,16 +4094,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9853</v>
+        <v>0.9835</v>
       </c>
       <c r="F115" t="n">
-        <v>1.3486</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="G115" t="n">
-        <v>76.2402</v>
+        <v>79.001</v>
       </c>
       <c r="H115" t="n">
-        <v>212.9236</v>
+        <v>221.2197</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9676</v>
+        <v>0.8617</v>
       </c>
       <c r="F116" t="n">
-        <v>1.8114</v>
+        <v>0.0623</v>
       </c>
       <c r="G116" t="n">
-        <v>127.1099</v>
+        <v>208.8407</v>
       </c>
       <c r="H116" t="n">
-        <v>324.8213</v>
+        <v>340.1268</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9646</v>
+        <v>0.8195</v>
       </c>
       <c r="F117" t="n">
-        <v>1.8531</v>
+        <v>0.0437</v>
       </c>
       <c r="G117" t="n">
-        <v>128.7401</v>
+        <v>234.1058</v>
       </c>
       <c r="H117" t="n">
-        <v>333.0583</v>
+        <v>343.4785</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9848</v>
+        <v>0.9716</v>
       </c>
       <c r="F118" t="n">
-        <v>1.3074</v>
+        <v>0.6337</v>
       </c>
       <c r="G118" t="n">
-        <v>74.0167</v>
+        <v>90.50620000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>199.9184</v>
+        <v>212.5833</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9867</v>
+        <v>0.9822</v>
       </c>
       <c r="F119" t="n">
-        <v>1.358</v>
+        <v>0.6054</v>
       </c>
       <c r="G119" t="n">
-        <v>77.8725</v>
+        <v>81.03100000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>215.7591</v>
+        <v>220.6248</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9789</v>
+        <v>0.9171</v>
       </c>
       <c r="F120" t="n">
-        <v>1.3922</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="G120" t="n">
-        <v>83.85039999999999</v>
+        <v>144.8038</v>
       </c>
       <c r="H120" t="n">
-        <v>225.8438</v>
+        <v>228.9392</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9789</v>
+        <v>0.9171</v>
       </c>
       <c r="F121" t="n">
-        <v>1.3922</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>83.85039999999999</v>
+        <v>144.8038</v>
       </c>
       <c r="H121" t="n">
-        <v>225.8438</v>
+        <v>228.9392</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9845</v>
+        <v>0.9811</v>
       </c>
       <c r="F122" t="n">
-        <v>1.3197</v>
+        <v>0.6161</v>
       </c>
       <c r="G122" t="n">
-        <v>74.5433</v>
+        <v>79.2127</v>
       </c>
       <c r="H122" t="n">
-        <v>203.8885</v>
+        <v>217.6278</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9866</v>
+        <v>0.9821</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3582</v>
+        <v>0.6056</v>
       </c>
       <c r="G123" t="n">
-        <v>77.87649999999999</v>
+        <v>81.11190000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>215.8218</v>
+        <v>220.5805</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.983</v>
       </c>
       <c r="F124" t="n">
-        <v>1.338</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="G124" t="n">
-        <v>74.173</v>
+        <v>76.67140000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>209.6501</v>
+        <v>211.73</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9862</v>
+        <v>0.9792</v>
       </c>
       <c r="F125" t="n">
-        <v>1.3256</v>
+        <v>0.6202</v>
       </c>
       <c r="G125" t="n">
-        <v>70.88500000000001</v>
+        <v>82.4102</v>
       </c>
       <c r="H125" t="n">
-        <v>205.7609</v>
+        <v>216.4483</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.984</v>
+        <v>0.9771</v>
       </c>
       <c r="F126" t="n">
-        <v>1.3886</v>
+        <v>0.5847</v>
       </c>
       <c r="G126" t="n">
-        <v>81.38509999999999</v>
+        <v>93.1277</v>
       </c>
       <c r="H126" t="n">
-        <v>224.794</v>
+        <v>226.342</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9865</v>
+        <v>0.9833</v>
       </c>
       <c r="F127" t="n">
-        <v>1.3289</v>
+        <v>0.632</v>
       </c>
       <c r="G127" t="n">
-        <v>72.99979999999999</v>
+        <v>76.49720000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>206.8062</v>
+        <v>213.0727</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
